--- a/artfynd/A 7996-2025 artfynd.xlsx
+++ b/artfynd/A 7996-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128652026</v>
       </c>
       <c r="B2" t="n">
-        <v>96179</v>
+        <v>96185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128652018</v>
       </c>
       <c r="B3" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128652007</v>
       </c>
       <c r="B5" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128652021</v>
       </c>
       <c r="B6" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128652000</v>
       </c>
       <c r="B7" t="n">
-        <v>92784</v>
+        <v>92790</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128652019</v>
       </c>
       <c r="B8" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 7996-2025 artfynd.xlsx
+++ b/artfynd/A 7996-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128652026</v>
       </c>
       <c r="B2" t="n">
-        <v>96185</v>
+        <v>96187</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128652018</v>
       </c>
       <c r="B3" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128652001</v>
       </c>
       <c r="B4" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128652007</v>
       </c>
       <c r="B5" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128652021</v>
       </c>
       <c r="B6" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128652000</v>
       </c>
       <c r="B7" t="n">
-        <v>92790</v>
+        <v>92792</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128652019</v>
       </c>
       <c r="B8" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 7996-2025 artfynd.xlsx
+++ b/artfynd/A 7996-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>128652007</v>
       </c>
       <c r="B5" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 7996-2025 artfynd.xlsx
+++ b/artfynd/A 7996-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128652026</v>
       </c>
       <c r="B2" t="n">
-        <v>96187</v>
+        <v>96188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128652018</v>
       </c>
       <c r="B3" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128652007</v>
       </c>
       <c r="B5" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128652021</v>
       </c>
       <c r="B6" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128652000</v>
       </c>
       <c r="B7" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128652019</v>
       </c>
       <c r="B8" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 7996-2025 artfynd.xlsx
+++ b/artfynd/A 7996-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128652026</v>
       </c>
       <c r="B2" t="n">
-        <v>96188</v>
+        <v>96215</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128652018</v>
       </c>
       <c r="B3" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128652001</v>
       </c>
       <c r="B4" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128652007</v>
       </c>
       <c r="B5" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128652021</v>
       </c>
       <c r="B6" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128652000</v>
       </c>
       <c r="B7" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128652019</v>
       </c>
       <c r="B8" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 7996-2025 artfynd.xlsx
+++ b/artfynd/A 7996-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128652026</v>
       </c>
       <c r="B2" t="n">
-        <v>96215</v>
+        <v>96221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128652018</v>
       </c>
       <c r="B3" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128652001</v>
       </c>
       <c r="B4" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128652007</v>
       </c>
       <c r="B5" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128652021</v>
       </c>
       <c r="B6" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128652000</v>
       </c>
       <c r="B7" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128652019</v>
       </c>
       <c r="B8" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 7996-2025 artfynd.xlsx
+++ b/artfynd/A 7996-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128652026</v>
       </c>
       <c r="B2" t="n">
-        <v>96221</v>
+        <v>96228</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128652018</v>
       </c>
       <c r="B3" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128652007</v>
       </c>
       <c r="B5" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128652021</v>
       </c>
       <c r="B6" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128652000</v>
       </c>
       <c r="B7" t="n">
-        <v>92825</v>
+        <v>92832</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128652019</v>
       </c>
       <c r="B8" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 7996-2025 artfynd.xlsx
+++ b/artfynd/A 7996-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128652026</v>
       </c>
       <c r="B2" t="n">
-        <v>96228</v>
+        <v>96232</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128652018</v>
       </c>
       <c r="B3" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128652001</v>
       </c>
       <c r="B4" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128652007</v>
       </c>
       <c r="B5" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128652021</v>
       </c>
       <c r="B6" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128652000</v>
       </c>
       <c r="B7" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128652019</v>
       </c>
       <c r="B8" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 7996-2025 artfynd.xlsx
+++ b/artfynd/A 7996-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128652026</v>
       </c>
       <c r="B2" t="n">
-        <v>96232</v>
+        <v>96239</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128652018</v>
       </c>
       <c r="B3" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128652001</v>
       </c>
       <c r="B4" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128652007</v>
       </c>
       <c r="B5" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128652021</v>
       </c>
       <c r="B6" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128652000</v>
       </c>
       <c r="B7" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128652019</v>
       </c>
       <c r="B8" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 7996-2025 artfynd.xlsx
+++ b/artfynd/A 7996-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128652026</v>
       </c>
       <c r="B2" t="n">
-        <v>96242</v>
+        <v>96247</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128652018</v>
       </c>
       <c r="B3" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128652001</v>
       </c>
       <c r="B4" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128652007</v>
       </c>
       <c r="B5" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128652021</v>
       </c>
       <c r="B6" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128652000</v>
       </c>
       <c r="B7" t="n">
-        <v>92844</v>
+        <v>92849</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128652019</v>
       </c>
       <c r="B8" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 7996-2025 artfynd.xlsx
+++ b/artfynd/A 7996-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128652026</v>
       </c>
       <c r="B2" t="n">
-        <v>96247</v>
+        <v>96255</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128652018</v>
       </c>
       <c r="B3" t="n">
-        <v>92811</v>
+        <v>92819</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128652001</v>
       </c>
       <c r="B4" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128652007</v>
       </c>
       <c r="B5" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128652021</v>
       </c>
       <c r="B6" t="n">
-        <v>92811</v>
+        <v>92819</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128652000</v>
       </c>
       <c r="B7" t="n">
-        <v>92849</v>
+        <v>92857</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128652019</v>
       </c>
       <c r="B8" t="n">
-        <v>92811</v>
+        <v>92819</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 7996-2025 artfynd.xlsx
+++ b/artfynd/A 7996-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128652026</v>
       </c>
       <c r="B2" t="n">
-        <v>96255</v>
+        <v>96265</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128652018</v>
       </c>
       <c r="B3" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128652001</v>
       </c>
       <c r="B4" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128652007</v>
       </c>
       <c r="B5" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128652021</v>
       </c>
       <c r="B6" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128652000</v>
       </c>
       <c r="B7" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128652019</v>
       </c>
       <c r="B8" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 7996-2025 artfynd.xlsx
+++ b/artfynd/A 7996-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1352,6 +1352,112 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129923087</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98790</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Tokilstjärn, NO om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>342020</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6576580</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sillerud</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>S-Årj-0425</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7996-2025 artfynd.xlsx
+++ b/artfynd/A 7996-2025 artfynd.xlsx
@@ -1357,7 +1357,7 @@
         <v>129923087</v>
       </c>
       <c r="B9" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 7996-2025 artfynd.xlsx
+++ b/artfynd/A 7996-2025 artfynd.xlsx
@@ -1357,7 +1357,7 @@
         <v>129923087</v>
       </c>
       <c r="B9" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 7996-2025 artfynd.xlsx
+++ b/artfynd/A 7996-2025 artfynd.xlsx
@@ -1357,7 +1357,7 @@
         <v>129923087</v>
       </c>
       <c r="B9" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 7996-2025 artfynd.xlsx
+++ b/artfynd/A 7996-2025 artfynd.xlsx
@@ -1357,7 +1357,7 @@
         <v>129923087</v>
       </c>
       <c r="B9" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 7996-2025 artfynd.xlsx
+++ b/artfynd/A 7996-2025 artfynd.xlsx
@@ -1357,7 +1357,7 @@
         <v>129923087</v>
       </c>
       <c r="B9" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 7996-2025 artfynd.xlsx
+++ b/artfynd/A 7996-2025 artfynd.xlsx
@@ -1357,7 +1357,7 @@
         <v>129923087</v>
       </c>
       <c r="B9" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 7996-2025 artfynd.xlsx
+++ b/artfynd/A 7996-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128652026</v>
+        <v>128652025</v>
       </c>
       <c r="B2" t="n">
-        <v>96265</v>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>342079</v>
+        <v>342257</v>
       </c>
       <c r="R2" t="n">
-        <v>6576551</v>
+        <v>6576411</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128652018</v>
+        <v>128652026</v>
       </c>
       <c r="B3" t="n">
-        <v>92826</v>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>342162</v>
+        <v>342079</v>
       </c>
       <c r="R3" t="n">
-        <v>6576297</v>
+        <v>6576551</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128652001</v>
+        <v>128652018</v>
       </c>
       <c r="B4" t="n">
-        <v>80144</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>342053</v>
+        <v>342162</v>
       </c>
       <c r="R4" t="n">
-        <v>6576575</v>
+        <v>6576297</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128652007</v>
+        <v>128652019</v>
       </c>
       <c r="B5" t="n">
-        <v>98669</v>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>342019</v>
+        <v>342055</v>
       </c>
       <c r="R5" t="n">
-        <v>6576580</v>
+        <v>6576317</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,11 +1066,11 @@
         <v>128652021</v>
       </c>
       <c r="B6" t="n">
-        <v>92826</v>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128652000</v>
+        <v>128651999</v>
       </c>
       <c r="B7" t="n">
-        <v>92864</v>
+        <v>93235</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>342147</v>
+        <v>342243</v>
       </c>
       <c r="R7" t="n">
-        <v>6576291</v>
+        <v>6576362</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128652019</v>
+        <v>128652000</v>
       </c>
       <c r="B8" t="n">
-        <v>92826</v>
+        <v>93235</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>342055</v>
+        <v>342147</v>
       </c>
       <c r="R8" t="n">
-        <v>6576317</v>
+        <v>6576291</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,45 +1354,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129923087</v>
+        <v>128652001</v>
       </c>
       <c r="B9" t="n">
-        <v>98920</v>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tokilstjärn, NO om, Vrm</t>
+          <t>Tokilstjärn, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>342020</v>
+        <v>342053</v>
       </c>
       <c r="R9" t="n">
-        <v>6576580</v>
+        <v>6576575</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1417,11 +1417,6 @@
           <t>Sillerud</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>S-Årj-0425</t>
-        </is>
-      </c>
       <c r="Y9" t="inlineStr">
         <is>
           <t>2025-09-23</t>
@@ -1444,15 +1439,408 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128652006</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Tokilstjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>342261</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6576401</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sillerud</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128651994</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Tokilstjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>342261</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6576401</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sillerud</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128652007</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tokilstjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>342019</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6576580</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sillerud</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129923087</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Tokilstjärn, NO om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>342020</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6576580</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sillerud</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>S-Årj-0425</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
           <t>Owe Nilsson</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>
